--- a/docs/alliance-import-templates/04-合作协议导入模板-mock数据.xlsx
+++ b/docs/alliance-import-templates/04-合作协议导入模板-mock数据.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>填写说明：
 * 必填列。
@@ -140,6 +140,48 @@
   </si>
   <si>
     <t>常州康健生物医药有限公司</t>
+  </si>
+  <si>
+    <t>工业机器人视觉质检系统研发</t>
+  </si>
+  <si>
+    <t>生物医药现代学徒制试点</t>
+  </si>
+  <si>
+    <t>智能装备制造专业群订单班培养协议</t>
+  </si>
+  <si>
+    <t>订单班培养</t>
+  </si>
+  <si>
+    <t>2025-08-01</t>
+  </si>
+  <si>
+    <t>2027-07-31</t>
+  </si>
+  <si>
+    <t>校企联合订单班培养，企业参与课程共建与实习实训</t>
+  </si>
+  <si>
+    <t>无锡智联教育装备有限公司</t>
+  </si>
+  <si>
+    <t>智能装备制造专业群人才共育</t>
+  </si>
+  <si>
+    <t>生物医药现代学徒制试点合作协议</t>
+  </si>
+  <si>
+    <t>现代学徒制</t>
+  </si>
+  <si>
+    <t>2026-08-01</t>
+  </si>
+  <si>
+    <t>2028-07-31</t>
+  </si>
+  <si>
+    <t>生物医药现代学徒制试点班合作办学协议</t>
   </si>
 </sst>
 </file>
@@ -550,7 +592,7 @@
         <v>15</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="true">
@@ -628,7 +670,59 @@
         <v>38</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>16</v>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/docs/alliance-import-templates/04-合作协议导入模板-mock数据.xlsx
+++ b/docs/alliance-import-templates/04-合作协议导入模板-mock数据.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>填写说明：
 * 必填列。
@@ -25,7 +25,8 @@
 开始日期 / 结束日期：格式 YYYY-MM-DD，选填
 状态：草稿 / 生效中 / 已失效 / 已续签 / 已终止（或 draft / active / expired / renewed / terminated），默认为 草稿
 内容：文本，选填
-【关联参考列】（青蓝色表头，导入时忽略）：关联企业 / 关联项目 为跨表单 mock 数据关联，多值用中文分号「；」分隔，需与对应导入模板中的名称保持一致</t>
+关联归属项目：项目名称，选填，多值用中文分号「；」分隔，按名称匹配导入
+关联合作企业：企业名称，选填，多值用中文分号「；」分隔，按名称匹配导入</t>
   </si>
   <si>
     <t>协议名称 *</t>
@@ -46,10 +47,10 @@
     <t>内容</t>
   </si>
   <si>
-    <t>关联企业名称</t>
-  </si>
-  <si>
-    <t>关联项目名称</t>
+    <t>关联归属项目</t>
+  </si>
+  <si>
+    <t>关联合作企业</t>
   </si>
   <si>
     <t>校企共建工业机器人视觉质检实验室协议</t>
@@ -70,12 +71,12 @@
     <t>共建视觉质检实验室，企业提供设备与工程师资源，学校提供场地与师资</t>
   </si>
   <si>
+    <t>工业机器人视觉质检系统研发</t>
+  </si>
+  <si>
     <t>苏州华芯智能制造有限公司</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>新能源汽车电控实训基地共建协议</t>
   </si>
   <si>
@@ -91,12 +92,12 @@
     <t>共建新能源汽车电控实训基地，含设备购置、课程共建与师资互聘</t>
   </si>
   <si>
+    <t>新能源汽车电控系统实训基地建设</t>
+  </si>
+  <si>
     <t>南京云驰新能源科技有限公司</t>
   </si>
   <si>
-    <t>新能源汽车电控系统实训基地建设</t>
-  </si>
-  <si>
     <t>产学研协同创新中心共建协议</t>
   </si>
   <si>
@@ -115,10 +116,52 @@
     <t>联合建设产学研协同创新中心，开展技术研发、成果转化与人才培养</t>
   </si>
   <si>
+    <t>工业互联网+智能制造协同创新中心</t>
+  </si>
+  <si>
     <t>苏州华芯智能制造有限公司；无锡智联教育装备有限公司</t>
   </si>
   <si>
-    <t>工业互联网+智能制造协同创新中心</t>
+    <t>智能装备制造专业群订单班培养协议</t>
+  </si>
+  <si>
+    <t>订单班培养</t>
+  </si>
+  <si>
+    <t>2025-08-01</t>
+  </si>
+  <si>
+    <t>2027-07-31</t>
+  </si>
+  <si>
+    <t>校企联合订单班培养，企业参与课程共建与实习实训</t>
+  </si>
+  <si>
+    <t>智能装备制造专业群人才共育</t>
+  </si>
+  <si>
+    <t>无锡智联教育装备有限公司</t>
+  </si>
+  <si>
+    <t>生物医药现代学徒制试点合作协议</t>
+  </si>
+  <si>
+    <t>现代学徒制</t>
+  </si>
+  <si>
+    <t>2026-08-01</t>
+  </si>
+  <si>
+    <t>2028-07-31</t>
+  </si>
+  <si>
+    <t>生物医药现代学徒制试点班合作办学协议</t>
+  </si>
+  <si>
+    <t>生物医药现代学徒制试点</t>
+  </si>
+  <si>
+    <t>常州康健生物医药有限公司</t>
   </si>
   <si>
     <t>生物医药企业实践基地合作意向书</t>
@@ -137,58 +180,13 @@
   </si>
   <si>
     <t>生物医药企业实践基地合作意向书（已到期未续签）</t>
-  </si>
-  <si>
-    <t>常州康健生物医药有限公司</t>
-  </si>
-  <si>
-    <t>工业机器人视觉质检系统研发</t>
-  </si>
-  <si>
-    <t>生物医药现代学徒制试点</t>
-  </si>
-  <si>
-    <t>智能装备制造专业群订单班培养协议</t>
-  </si>
-  <si>
-    <t>订单班培养</t>
-  </si>
-  <si>
-    <t>2025-08-01</t>
-  </si>
-  <si>
-    <t>2027-07-31</t>
-  </si>
-  <si>
-    <t>校企联合订单班培养，企业参与课程共建与实习实训</t>
-  </si>
-  <si>
-    <t>无锡智联教育装备有限公司</t>
-  </si>
-  <si>
-    <t>智能装备制造专业群人才共育</t>
-  </si>
-  <si>
-    <t>生物医药现代学徒制试点合作协议</t>
-  </si>
-  <si>
-    <t>现代学徒制</t>
-  </si>
-  <si>
-    <t>2026-08-01</t>
-  </si>
-  <si>
-    <t>2028-07-31</t>
-  </si>
-  <si>
-    <t>生物医药现代学徒制试点班合作办学协议</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -205,13 +203,8 @@
       <color rgb="FF595959"/>
       <sz val="10"/>
     </font>
-    <font>
-      <family val="2"/>
-      <color rgb="FF2E74B5"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -221,6 +214,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E74B5"/>
       </patternFill>
     </fill>
     <fill>
@@ -246,10 +244,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
-      <alignment vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment vertical="center" wrapText="true"/>
     </xf>
   </cellXfs>
@@ -527,21 +525,21 @@
     <col customWidth="true" max="4" min="3" width="16"/>
     <col customWidth="true" max="5" min="5" width="20"/>
     <col customWidth="true" max="6" min="6" width="48"/>
-    <col customWidth="true" max="7" min="7" width="32"/>
-    <col customWidth="true" max="8" min="8" width="36"/>
+    <col customWidth="true" max="7" min="7" width="36"/>
+    <col customWidth="true" max="8" min="8" width="40"/>
   </cols>
   <sheetData>
     <row r="1" ht="165" customHeight="true">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
     </row>
     <row r="2" ht="26" customHeight="true">
       <c r="A2" s="1" t="s">
@@ -562,10 +560,10 @@
       <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="1" t="s">
         <v>8</v>
       </c>
     </row>
@@ -588,11 +586,11 @@
       <c r="F3" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>39</v>
+      <c r="H3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="true">
@@ -614,10 +612,10 @@
       <c r="F4" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" t="s">
         <v>23</v>
       </c>
     </row>
@@ -640,10 +638,10 @@
       <c r="F5" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" t="s">
         <v>30</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" t="s">
         <v>31</v>
       </c>
     </row>
@@ -661,68 +659,68 @@
         <v>35</v>
       </c>
       <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" t="s">
         <v>36</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>37</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" t="s">
         <v>38</v>
       </c>
-      <c r="H6" s="3" t="s">
+    </row>
+    <row r="7" ht="20" customHeight="true">
+      <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
         <v>40</v>
       </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" t="s">
+        <v>45</v>
+      </c>
     </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" t="s">
+    <row r="8" ht="20" customHeight="true">
+      <c r="A8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" t="s">
         <v>44</v>
       </c>
-      <c r="E7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="H8" t="s">
         <v>45</v>
-      </c>
-      <c r="G7" t="s">
-        <v>46</v>
-      </c>
-      <c r="H7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" t="s">
-        <v>52</v>
-      </c>
-      <c r="G8" t="s">
-        <v>38</v>
-      </c>
-      <c r="H8" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
